--- a/MiniTemplate/Datas/function.xlsx
+++ b/MiniTemplate/Datas/function.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,24 @@
         <v>4028</v>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CommunityCentreNotice</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>???????</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MiniTemplate/Datas/function.xlsx
+++ b/MiniTemplate/Datas/function.xlsx
@@ -2,27 +2,33 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="function" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -50,7 +56,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +419,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -647,13 +653,49 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>???????</t>
+          <t>社区中心布告</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1003</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VendingMachine</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>自动售货机</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LostWallet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>遗失的钱包</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E13" t="n">
         <v>0</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/function.xlsx
+++ b/MiniTemplate/Datas/function.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -699,6 +699,42 @@
         <v>0</v>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>StrayCatFoodBowl</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>流浪猫食物盆</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Donation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>社区募捐箱</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MiniTemplate/Datas/function.xlsx
+++ b/MiniTemplate/Datas/function.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,6 +427,8 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,6 +457,16 @@
           <t>unlockItemId</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>unlockAge</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>unlockMonth</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -482,6 +494,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,6 +531,16 @@
           <t>c,s</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -536,6 +568,16 @@
           <t>解锁道具 ID；0 表示不需要道具</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>解锁所需年龄；0 表示不限制</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>解锁所需月份；0 表示不限制</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -549,10 +591,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1003</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>22</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -572,6 +620,12 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -590,6 +644,12 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -608,6 +668,12 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -626,6 +692,12 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -644,6 +716,12 @@
       <c r="E10" t="n">
         <v>4028</v>
       </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -662,6 +740,12 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -680,6 +764,12 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -698,6 +788,12 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -716,6 +812,12 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -732,6 +834,12 @@
         <v>1003</v>
       </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/function.xlsx
+++ b/MiniTemplate/Datas/function.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -841,6 +841,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CommunityCentreNoticeMission3005</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>布告鹿伯安委托</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>201</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MiniTemplate/Datas/function.xlsx
+++ b/MiniTemplate/Datas/function.xlsx
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1003</v>
+        <v>201</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
